--- a/etsy/debt-payoff/Plan-Remboursement-Dettes.xlsx
+++ b/etsy/debt-payoff/Plan-Remboursement-Dettes.xlsx
@@ -141,7 +141,7 @@
       <sz val="13"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -150,8 +150,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F6F4EF"/>
-        <bgColor rgb="00F6F4EF"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -164,12 +164,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFF4C2"/>
         <bgColor rgb="00FFF4C2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -195,16 +189,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D9D4C7"/>
+        <color rgb="00D5DBDB"/>
       </left>
       <right style="thin">
-        <color rgb="00D9D4C7"/>
+        <color rgb="00D5DBDB"/>
       </right>
       <top style="thin">
-        <color rgb="00D9D4C7"/>
+        <color rgb="00D5DBDB"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D9D4C7"/>
+        <color rgb="00D5DBDB"/>
       </bottom>
     </border>
   </borders>
@@ -216,39 +210,39 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="13" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="14" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="14" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="15" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="13" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="14" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="14" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="15" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -259,7 +253,7 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -380,7 +374,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Regardez chaque dette disparaître</a:t>
+              <a:t>Ce que vous devez sur chaque dette</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1066,7 +1060,7 @@
       <c r="A2" s="1" t="n"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Votre sortie de l’endettement</t>
+          <t>Votre plan de remboursement</t>
         </is>
       </c>
       <c r="C2" s="1" t="n"/>
@@ -1083,7 +1077,7 @@
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Changez la méthode ou le montant en plus dans l’onglet Dettes : tout se met à jour.</t>
+          <t>Changez la méthode ou le montant en plus dans l'onglet Dettes et tout se met à jour.</t>
         </is>
       </c>
       <c r="C3" s="1" t="n"/>
@@ -1216,7 +1210,7 @@
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="11">
-        <f>IFERROR("Payez le minimum sur chaque dette, et "&amp;FIXED(INDEX(Dettes!$H$6:$H$15,MATCH(1,IF(Dettes!$J$10="Boule de neige",Dettes!$F$6:$F$15,Dettes!$G$6:$G$15),0)),2)&amp;" sur "&amp;INDEX(Dettes!$B$6:$B$15,MATCH(1,IF(Dettes!$J$10="Boule de neige",Dettes!$F$6:$F$15,Dettes!$G$6:$G$15),0))&amp;". C’est votre dette prioritaire.","Ajoutez vos dettes dans l’onglet Dettes.")</f>
+        <f>IFERROR("Payez le minimum sur chaque dette, et "&amp;FIXED(INDEX(Dettes!$H$6:$H$15,MATCH(1,IF(Dettes!$J$10="Boule de neige",Dettes!$F$6:$F$15,Dettes!$G$6:$G$15),0)),2)&amp;" sur "&amp;INDEX(Dettes!$B$6:$B$15,MATCH(1,IF(Dettes!$J$10="Boule de neige",Dettes!$F$6:$F$15,Dettes!$G$6:$G$15),0))&amp;". C'est votre dette prioritaire.","Ajoutez vos dettes dans l'onglet Dettes.")</f>
         <v/>
       </c>
       <c r="G10" s="1" t="n"/>
@@ -1291,7 +1285,7 @@
         <v/>
       </c>
       <c r="F13" s="17">
-        <f>IF(E14-E13&gt;0.5,"économise "&amp;FIXED(E14-E13,0)&amp;" d’intérêts","mêmes intérêts")</f>
+        <f>IF(E14-E13&gt;0.5,"économise "&amp;FIXED(E14-E13,0)&amp;" d'intérêts","mêmes intérêts")</f>
         <v/>
       </c>
       <c r="G13" s="1" t="n"/>
@@ -2908,7 +2902,7 @@
       </c>
       <c r="J15" s="27" t="inlineStr">
         <is>
-          <t>Avalanche : le taux le plus élevé d’abord (le moins d’intérêts).</t>
+          <t>Avalanche : le taux le plus élevé d'abord (le moins d'intérêts).</t>
         </is>
       </c>
       <c r="K15" s="1" t="n"/>
@@ -2944,7 +2938,7 @@
       <c r="I16" s="1" t="n"/>
       <c r="J16" s="27" t="inlineStr">
         <is>
-          <t>Boule de neige : le plus petit solde d’abord (victoires rapides).</t>
+          <t>Boule de neige : le plus petit solde d'abord (victoires rapides).</t>
         </is>
       </c>
       <c r="K16" s="1" t="n"/>
@@ -4347,11 +4341,11 @@
         </is>
       </c>
       <c r="H6" s="31">
-        <f>IF(Dettes!$B$6="","",Dettes!$B$6&amp;" · due")</f>
+        <f>IF(Dettes!$B$6="","",Dettes!$B$6&amp;" (due)")</f>
         <v/>
       </c>
       <c r="I6" s="31">
-        <f>IF(Dettes!$B$6="","",Dettes!$B$6&amp;" · rem")</f>
+        <f>IF(Dettes!$B$6="","",Dettes!$B$6&amp;" (rem)")</f>
         <v/>
       </c>
       <c r="J6" s="32">
@@ -4359,11 +4353,11 @@
         <v/>
       </c>
       <c r="K6" s="31">
-        <f>IF(Dettes!$B$7="","",Dettes!$B$7&amp;" · due")</f>
+        <f>IF(Dettes!$B$7="","",Dettes!$B$7&amp;" (due)")</f>
         <v/>
       </c>
       <c r="L6" s="31">
-        <f>IF(Dettes!$B$7="","",Dettes!$B$7&amp;" · rem")</f>
+        <f>IF(Dettes!$B$7="","",Dettes!$B$7&amp;" (rem)")</f>
         <v/>
       </c>
       <c r="M6" s="32">
@@ -4371,11 +4365,11 @@
         <v/>
       </c>
       <c r="N6" s="31">
-        <f>IF(Dettes!$B$8="","",Dettes!$B$8&amp;" · due")</f>
+        <f>IF(Dettes!$B$8="","",Dettes!$B$8&amp;" (due)")</f>
         <v/>
       </c>
       <c r="O6" s="31">
-        <f>IF(Dettes!$B$8="","",Dettes!$B$8&amp;" · rem")</f>
+        <f>IF(Dettes!$B$8="","",Dettes!$B$8&amp;" (rem)")</f>
         <v/>
       </c>
       <c r="P6" s="32">
@@ -4383,11 +4377,11 @@
         <v/>
       </c>
       <c r="Q6" s="31">
-        <f>IF(Dettes!$B$9="","",Dettes!$B$9&amp;" · due")</f>
+        <f>IF(Dettes!$B$9="","",Dettes!$B$9&amp;" (due)")</f>
         <v/>
       </c>
       <c r="R6" s="31">
-        <f>IF(Dettes!$B$9="","",Dettes!$B$9&amp;" · rem")</f>
+        <f>IF(Dettes!$B$9="","",Dettes!$B$9&amp;" (rem)")</f>
         <v/>
       </c>
       <c r="S6" s="32">
@@ -4395,11 +4389,11 @@
         <v/>
       </c>
       <c r="T6" s="31">
-        <f>IF(Dettes!$B$10="","",Dettes!$B$10&amp;" · due")</f>
+        <f>IF(Dettes!$B$10="","",Dettes!$B$10&amp;" (due)")</f>
         <v/>
       </c>
       <c r="U6" s="31">
-        <f>IF(Dettes!$B$10="","",Dettes!$B$10&amp;" · rem")</f>
+        <f>IF(Dettes!$B$10="","",Dettes!$B$10&amp;" (rem)")</f>
         <v/>
       </c>
       <c r="V6" s="32">
@@ -4407,11 +4401,11 @@
         <v/>
       </c>
       <c r="W6" s="31">
-        <f>IF(Dettes!$B$11="","",Dettes!$B$11&amp;" · due")</f>
+        <f>IF(Dettes!$B$11="","",Dettes!$B$11&amp;" (due)")</f>
         <v/>
       </c>
       <c r="X6" s="31">
-        <f>IF(Dettes!$B$11="","",Dettes!$B$11&amp;" · rem")</f>
+        <f>IF(Dettes!$B$11="","",Dettes!$B$11&amp;" (rem)")</f>
         <v/>
       </c>
       <c r="Y6" s="32">
@@ -4419,11 +4413,11 @@
         <v/>
       </c>
       <c r="Z6" s="31">
-        <f>IF(Dettes!$B$12="","",Dettes!$B$12&amp;" · due")</f>
+        <f>IF(Dettes!$B$12="","",Dettes!$B$12&amp;" (due)")</f>
         <v/>
       </c>
       <c r="AA6" s="31">
-        <f>IF(Dettes!$B$12="","",Dettes!$B$12&amp;" · rem")</f>
+        <f>IF(Dettes!$B$12="","",Dettes!$B$12&amp;" (rem)")</f>
         <v/>
       </c>
       <c r="AB6" s="32">
@@ -4431,11 +4425,11 @@
         <v/>
       </c>
       <c r="AC6" s="31">
-        <f>IF(Dettes!$B$13="","",Dettes!$B$13&amp;" · due")</f>
+        <f>IF(Dettes!$B$13="","",Dettes!$B$13&amp;" (due)")</f>
         <v/>
       </c>
       <c r="AD6" s="31">
-        <f>IF(Dettes!$B$13="","",Dettes!$B$13&amp;" · rem")</f>
+        <f>IF(Dettes!$B$13="","",Dettes!$B$13&amp;" (rem)")</f>
         <v/>
       </c>
       <c r="AE6" s="32">
@@ -4443,11 +4437,11 @@
         <v/>
       </c>
       <c r="AF6" s="31">
-        <f>IF(Dettes!$B$14="","",Dettes!$B$14&amp;" · due")</f>
+        <f>IF(Dettes!$B$14="","",Dettes!$B$14&amp;" (due)")</f>
         <v/>
       </c>
       <c r="AG6" s="31">
-        <f>IF(Dettes!$B$14="","",Dettes!$B$14&amp;" · rem")</f>
+        <f>IF(Dettes!$B$14="","",Dettes!$B$14&amp;" (rem)")</f>
         <v/>
       </c>
       <c r="AH6" s="32">
@@ -4455,11 +4449,11 @@
         <v/>
       </c>
       <c r="AI6" s="31">
-        <f>IF(Dettes!$B$15="","",Dettes!$B$15&amp;" · due")</f>
+        <f>IF(Dettes!$B$15="","",Dettes!$B$15&amp;" (due)")</f>
         <v/>
       </c>
       <c r="AJ6" s="31">
-        <f>IF(Dettes!$B$15="","",Dettes!$B$15&amp;" · rem")</f>
+        <f>IF(Dettes!$B$15="","",Dettes!$B$15&amp;" (rem)")</f>
         <v/>
       </c>
       <c r="AK6" s="32">
@@ -31553,11 +31547,11 @@
         </is>
       </c>
       <c r="H6" s="31">
-        <f>IF(Dettes!$B$6="","",Dettes!$B$6&amp;" · due")</f>
+        <f>IF(Dettes!$B$6="","",Dettes!$B$6&amp;" (due)")</f>
         <v/>
       </c>
       <c r="I6" s="31">
-        <f>IF(Dettes!$B$6="","",Dettes!$B$6&amp;" · rem")</f>
+        <f>IF(Dettes!$B$6="","",Dettes!$B$6&amp;" (rem)")</f>
         <v/>
       </c>
       <c r="J6" s="32">
@@ -31565,11 +31559,11 @@
         <v/>
       </c>
       <c r="K6" s="31">
-        <f>IF(Dettes!$B$7="","",Dettes!$B$7&amp;" · due")</f>
+        <f>IF(Dettes!$B$7="","",Dettes!$B$7&amp;" (due)")</f>
         <v/>
       </c>
       <c r="L6" s="31">
-        <f>IF(Dettes!$B$7="","",Dettes!$B$7&amp;" · rem")</f>
+        <f>IF(Dettes!$B$7="","",Dettes!$B$7&amp;" (rem)")</f>
         <v/>
       </c>
       <c r="M6" s="32">
@@ -31577,11 +31571,11 @@
         <v/>
       </c>
       <c r="N6" s="31">
-        <f>IF(Dettes!$B$8="","",Dettes!$B$8&amp;" · due")</f>
+        <f>IF(Dettes!$B$8="","",Dettes!$B$8&amp;" (due)")</f>
         <v/>
       </c>
       <c r="O6" s="31">
-        <f>IF(Dettes!$B$8="","",Dettes!$B$8&amp;" · rem")</f>
+        <f>IF(Dettes!$B$8="","",Dettes!$B$8&amp;" (rem)")</f>
         <v/>
       </c>
       <c r="P6" s="32">
@@ -31589,11 +31583,11 @@
         <v/>
       </c>
       <c r="Q6" s="31">
-        <f>IF(Dettes!$B$9="","",Dettes!$B$9&amp;" · due")</f>
+        <f>IF(Dettes!$B$9="","",Dettes!$B$9&amp;" (due)")</f>
         <v/>
       </c>
       <c r="R6" s="31">
-        <f>IF(Dettes!$B$9="","",Dettes!$B$9&amp;" · rem")</f>
+        <f>IF(Dettes!$B$9="","",Dettes!$B$9&amp;" (rem)")</f>
         <v/>
       </c>
       <c r="S6" s="32">
@@ -31601,11 +31595,11 @@
         <v/>
       </c>
       <c r="T6" s="31">
-        <f>IF(Dettes!$B$10="","",Dettes!$B$10&amp;" · due")</f>
+        <f>IF(Dettes!$B$10="","",Dettes!$B$10&amp;" (due)")</f>
         <v/>
       </c>
       <c r="U6" s="31">
-        <f>IF(Dettes!$B$10="","",Dettes!$B$10&amp;" · rem")</f>
+        <f>IF(Dettes!$B$10="","",Dettes!$B$10&amp;" (rem)")</f>
         <v/>
       </c>
       <c r="V6" s="32">
@@ -31613,11 +31607,11 @@
         <v/>
       </c>
       <c r="W6" s="31">
-        <f>IF(Dettes!$B$11="","",Dettes!$B$11&amp;" · due")</f>
+        <f>IF(Dettes!$B$11="","",Dettes!$B$11&amp;" (due)")</f>
         <v/>
       </c>
       <c r="X6" s="31">
-        <f>IF(Dettes!$B$11="","",Dettes!$B$11&amp;" · rem")</f>
+        <f>IF(Dettes!$B$11="","",Dettes!$B$11&amp;" (rem)")</f>
         <v/>
       </c>
       <c r="Y6" s="32">
@@ -31625,11 +31619,11 @@
         <v/>
       </c>
       <c r="Z6" s="31">
-        <f>IF(Dettes!$B$12="","",Dettes!$B$12&amp;" · due")</f>
+        <f>IF(Dettes!$B$12="","",Dettes!$B$12&amp;" (due)")</f>
         <v/>
       </c>
       <c r="AA6" s="31">
-        <f>IF(Dettes!$B$12="","",Dettes!$B$12&amp;" · rem")</f>
+        <f>IF(Dettes!$B$12="","",Dettes!$B$12&amp;" (rem)")</f>
         <v/>
       </c>
       <c r="AB6" s="32">
@@ -31637,11 +31631,11 @@
         <v/>
       </c>
       <c r="AC6" s="31">
-        <f>IF(Dettes!$B$13="","",Dettes!$B$13&amp;" · due")</f>
+        <f>IF(Dettes!$B$13="","",Dettes!$B$13&amp;" (due)")</f>
         <v/>
       </c>
       <c r="AD6" s="31">
-        <f>IF(Dettes!$B$13="","",Dettes!$B$13&amp;" · rem")</f>
+        <f>IF(Dettes!$B$13="","",Dettes!$B$13&amp;" (rem)")</f>
         <v/>
       </c>
       <c r="AE6" s="32">
@@ -31649,11 +31643,11 @@
         <v/>
       </c>
       <c r="AF6" s="31">
-        <f>IF(Dettes!$B$14="","",Dettes!$B$14&amp;" · due")</f>
+        <f>IF(Dettes!$B$14="","",Dettes!$B$14&amp;" (due)")</f>
         <v/>
       </c>
       <c r="AG6" s="31">
-        <f>IF(Dettes!$B$14="","",Dettes!$B$14&amp;" · rem")</f>
+        <f>IF(Dettes!$B$14="","",Dettes!$B$14&amp;" (rem)")</f>
         <v/>
       </c>
       <c r="AH6" s="32">
@@ -31661,11 +31655,11 @@
         <v/>
       </c>
       <c r="AI6" s="31">
-        <f>IF(Dettes!$B$15="","",Dettes!$B$15&amp;" · due")</f>
+        <f>IF(Dettes!$B$15="","",Dettes!$B$15&amp;" (due)")</f>
         <v/>
       </c>
       <c r="AJ6" s="31">
-        <f>IF(Dettes!$B$15="","",Dettes!$B$15&amp;" · rem")</f>
+        <f>IF(Dettes!$B$15="","",Dettes!$B$15&amp;" (rem)")</f>
         <v/>
       </c>
       <c r="AK6" s="32">
@@ -60550,7 +60544,7 @@
       <c r="A2" s="1" t="n"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Commencer ici : 3 minutes</t>
+          <t>Commencer ici</t>
         </is>
       </c>
       <c r="C2" s="1" t="n"/>
@@ -60560,7 +60554,7 @@
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Tapez uniquement dans les cases JAUNES.</t>
+          <t>Tapez uniquement dans les cases jaunes. Tout le reste est calculé.</t>
         </is>
       </c>
       <c r="C3" s="1" t="n"/>
@@ -60581,7 +60575,7 @@
       </c>
       <c r="C5" s="36" t="inlineStr">
         <is>
-          <t>Onglet Dettes : une ligne par dette : solde, taux annuel %, paiement minimum.</t>
+          <t>Onglet Dettes : une ligne par dette, avec le solde, le taux annuel et le paiement minimum.</t>
         </is>
       </c>
       <c r="D5" s="1" t="n"/>
@@ -60601,7 +60595,7 @@
       </c>
       <c r="C7" s="36" t="inlineStr">
         <is>
-          <t>Onglet Dettes : combien vous pouvez payer EN PLUS chaque mois (même 20 aide), et le mois du premier paiement.</t>
+          <t>Onglet Dettes : le montant en plus que vous pouvez payer chaque mois (même 20 aide) et le mois du premier paiement.</t>
         </is>
       </c>
       <c r="D7" s="1" t="n"/>
@@ -60621,7 +60615,7 @@
       </c>
       <c r="C9" s="36" t="inlineStr">
         <is>
-          <t>Choisissez une méthode : Avalanche (moins d’intérêts) ou Boule de neige (victoires rapides). Le Tableau de bord compare les deux.</t>
+          <t>Choisissez une méthode : Avalanche paie le moins d'intérêts, Boule de neige solde d'abord les petites dettes.</t>
         </is>
       </c>
       <c r="D9" s="1" t="n"/>
@@ -60636,12 +60630,12 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C11" s="36" t="inlineStr">
         <is>
-          <t>Tableau de bord : votre date de liberté, et UNE chose à faire ce mois-ci : quelle dette reçoit l’argent en plus.</t>
+          <t>Tableau de bord : la date où vous n'aurez plus de dettes, et la dette qui reçoit l'argent en plus ce mois-ci.</t>
         </is>
       </c>
       <c r="D11" s="1" t="n"/>
@@ -60656,12 +60650,12 @@
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>↻</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C13" s="36" t="inlineStr">
         <is>
-          <t>Chaque mois : mettez à jour les soldes d’après vos relevés. Le plan se recalcule.</t>
+          <t>Chaque mois, mettez à jour les soldes d'après vos relevés. Le plan est recalculé.</t>
         </is>
       </c>
       <c r="D13" s="1" t="n"/>
@@ -60689,7 +60683,7 @@
       <c r="B17" s="1" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Les onglets Snowball et Avalanche montrent le plan mois par mois. Case verte = le mois où une dette disparaît.</t>
+          <t>Les onglets Snowball et Avalanche montrent le plan mois par mois. Une case verte marque le mois où une dette est soldée.</t>
         </is>
       </c>
       <c r="D17" s="1" t="n"/>
@@ -60705,7 +60699,7 @@
       <c r="B19" s="1" t="n"/>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Outil de planification, pas un conseil financier. Fonctionne dans Google Sheets et Microsoft Excel.</t>
+          <t>C'est un outil de planification : il ne donne pas de conseil financier. Fonctionne dans Google Sheets et Microsoft Excel.</t>
         </is>
       </c>
       <c r="D19" s="1" t="n"/>
